--- a/assets/data/DLT历史数据_适配模型版.xlsx
+++ b/assets/data/DLT历史数据_适配模型版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2883"/>
+  <dimension ref="A1:H2885"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75402,6 +75402,58 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2884">
+      <c r="A2884" t="n">
+        <v>26065</v>
+      </c>
+      <c r="B2884" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2884" t="n">
+        <v>11</v>
+      </c>
+      <c r="D2884" t="n">
+        <v>12</v>
+      </c>
+      <c r="E2884" t="n">
+        <v>13</v>
+      </c>
+      <c r="F2884" t="n">
+        <v>25</v>
+      </c>
+      <c r="G2884" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2884" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2885">
+      <c r="A2885" t="n">
+        <v>26066</v>
+      </c>
+      <c r="B2885" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2885" t="n">
+        <v>13</v>
+      </c>
+      <c r="D2885" t="n">
+        <v>19</v>
+      </c>
+      <c r="E2885" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2885" t="n">
+        <v>30</v>
+      </c>
+      <c r="G2885" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2885" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>

--- a/assets/data/DLT历史数据_适配模型版.xlsx
+++ b/assets/data/DLT历史数据_适配模型版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2888"/>
+  <dimension ref="A1:H2889"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75532,6 +75532,32 @@
         <v>10</v>
       </c>
     </row>
+    <row r="2889">
+      <c r="A2889" t="n">
+        <v>26070</v>
+      </c>
+      <c r="B2889" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2889" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2889" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2889" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2889" t="n">
+        <v>32</v>
+      </c>
+      <c r="G2889" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2889" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>

--- a/assets/data/DLT历史数据_适配模型版.xlsx
+++ b/assets/data/DLT历史数据_适配模型版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2890"/>
+  <dimension ref="A1:H2894"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75584,6 +75584,110 @@
         <v>3</v>
       </c>
     </row>
+    <row r="2891">
+      <c r="A2891" t="n">
+        <v>26072</v>
+      </c>
+      <c r="B2891" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2891" t="n">
+        <v>13</v>
+      </c>
+      <c r="D2891" t="n">
+        <v>26</v>
+      </c>
+      <c r="E2891" t="n">
+        <v>29</v>
+      </c>
+      <c r="F2891" t="n">
+        <v>30</v>
+      </c>
+      <c r="G2891" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2891" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2892">
+      <c r="A2892" t="n">
+        <v>26073</v>
+      </c>
+      <c r="B2892" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2892" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2892" t="n">
+        <v>22</v>
+      </c>
+      <c r="E2892" t="n">
+        <v>23</v>
+      </c>
+      <c r="F2892" t="n">
+        <v>33</v>
+      </c>
+      <c r="G2892" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2892" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2893">
+      <c r="A2893" t="n">
+        <v>26074</v>
+      </c>
+      <c r="B2893" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2893" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2893" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2893" t="n">
+        <v>23</v>
+      </c>
+      <c r="F2893" t="n">
+        <v>25</v>
+      </c>
+      <c r="G2893" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2893" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2894">
+      <c r="A2894" t="n">
+        <v>26075</v>
+      </c>
+      <c r="B2894" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2894" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2894" t="n">
+        <v>16</v>
+      </c>
+      <c r="E2894" t="n">
+        <v>18</v>
+      </c>
+      <c r="F2894" t="n">
+        <v>26</v>
+      </c>
+      <c r="G2894" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2894" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>

--- a/assets/data/DLT历史数据_适配模型版.xlsx
+++ b/assets/data/DLT历史数据_适配模型版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2894"/>
+  <dimension ref="A1:H2898"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75688,6 +75688,110 @@
         <v>10</v>
       </c>
     </row>
+    <row r="2895">
+      <c r="A2895" t="n">
+        <v>26076</v>
+      </c>
+      <c r="B2895" t="n">
+        <v>15</v>
+      </c>
+      <c r="C2895" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2895" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2895" t="n">
+        <v>28</v>
+      </c>
+      <c r="F2895" t="n">
+        <v>35</v>
+      </c>
+      <c r="G2895" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2895" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2896">
+      <c r="A2896" t="n">
+        <v>26077</v>
+      </c>
+      <c r="B2896" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2896" t="n">
+        <v>14</v>
+      </c>
+      <c r="D2896" t="n">
+        <v>19</v>
+      </c>
+      <c r="E2896" t="n">
+        <v>24</v>
+      </c>
+      <c r="F2896" t="n">
+        <v>27</v>
+      </c>
+      <c r="G2896" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2896" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2897">
+      <c r="A2897" t="n">
+        <v>26078</v>
+      </c>
+      <c r="B2897" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2897" t="n">
+        <v>13</v>
+      </c>
+      <c r="D2897" t="n">
+        <v>20</v>
+      </c>
+      <c r="E2897" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2897" t="n">
+        <v>32</v>
+      </c>
+      <c r="G2897" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2897" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2898">
+      <c r="A2898" t="n">
+        <v>26079</v>
+      </c>
+      <c r="B2898" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2898" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2898" t="n">
+        <v>23</v>
+      </c>
+      <c r="E2898" t="n">
+        <v>26</v>
+      </c>
+      <c r="F2898" t="n">
+        <v>27</v>
+      </c>
+      <c r="G2898" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2898" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
